--- a/Measurement_Results/IC_Simulation/SE_OTA/SE_OTA_Full_PVT_Table.xlsx
+++ b/Measurement_Results/IC_Simulation/SE_OTA/SE_OTA_Full_PVT_Table.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6952" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6930" uniqueCount="80">
   <si>
     <t>Parameter</t>
   </si>
   <si>
-    <t>AVDD 3.3 V</t>
+    <t>AVDD</t>
   </si>
   <si>
     <t>Bias current</t>
@@ -105,9 +105,6 @@
     <t>PSRR- @ 1 kHz</t>
   </si>
   <si>
-    <t>Monte Carlo offset</t>
-  </si>
-  <si>
     <t>Unit</t>
   </si>
   <si>
@@ -153,496 +150,109 @@
     <t>40.000</t>
   </si>
   <si>
-    <t>284.406</t>
-  </si>
-  <si>
-    <t>0.9385</t>
+    <t>280.345</t>
+  </si>
+  <si>
+    <t>0.9251</t>
   </si>
   <si>
     <t>1.6500</t>
   </si>
   <si>
-    <t>0.033–2.958</t>
-  </si>
-  <si>
-    <t>0.042–2.968</t>
+    <t>0.000–2.440</t>
+  </si>
+  <si>
+    <t>0.041–2.998</t>
   </si>
   <si>
     <t>92.54</t>
   </si>
   <si>
-    <t>9.4023</t>
-  </si>
-  <si>
-    <t>178.01</t>
+    <t>9.5191</t>
+  </si>
+  <si>
+    <t>66.35</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>7.387</t>
-  </si>
-  <si>
-    <t>7.743</t>
-  </si>
-  <si>
-    <t>149.48</t>
-  </si>
-  <si>
-    <t>12.881</t>
-  </si>
-  <si>
-    <t>-0.003</t>
-  </si>
-  <si>
-    <t>107.95</t>
-  </si>
-  <si>
-    <t>104.00</t>
-  </si>
-  <si>
-    <t>103.97</t>
-  </si>
-  <si>
-    <t>161.90</t>
+    <t>7.470</t>
+  </si>
+  <si>
+    <t>7.752</t>
+  </si>
+  <si>
+    <t>147.07</t>
+  </si>
+  <si>
+    <t>12.594</t>
+  </si>
+  <si>
+    <t>0.253</t>
+  </si>
+  <si>
+    <t>107.86</t>
+  </si>
+  <si>
+    <t>107.60</t>
+  </si>
+  <si>
+    <t>107.56</t>
+  </si>
+  <si>
+    <t>107.61</t>
+  </si>
+  <si>
+    <t>107.58</t>
+  </si>
+  <si>
+    <t>ff</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>ff</t>
-  </si>
-  <si>
-    <t>285.137</t>
-  </si>
-  <si>
-    <t>0.9410</t>
-  </si>
-  <si>
-    <t>0.030–3.074</t>
-  </si>
-  <si>
-    <t>0.040–3.084</t>
-  </si>
-  <si>
-    <t>92.62</t>
-  </si>
-  <si>
-    <t>9.7595</t>
-  </si>
-  <si>
-    <t>178.02</t>
-  </si>
-  <si>
-    <t>7.421</t>
-  </si>
-  <si>
-    <t>7.775</t>
-  </si>
-  <si>
-    <t>148.65</t>
-  </si>
-  <si>
-    <t>12.159</t>
-  </si>
-  <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>109.56</t>
-  </si>
-  <si>
-    <t>104.48</t>
-  </si>
-  <si>
-    <t>104.46</t>
-  </si>
-  <si>
-    <t>162.01</t>
-  </si>
-  <si>
     <t>ss</t>
   </si>
   <si>
-    <t>283.660</t>
-  </si>
-  <si>
-    <t>0.9361</t>
-  </si>
-  <si>
-    <t>0.036–2.840</t>
-  </si>
-  <si>
-    <t>0.045–2.850</t>
-  </si>
-  <si>
-    <t>92.03</t>
-  </si>
-  <si>
-    <t>9.0551</t>
-  </si>
-  <si>
-    <t>178.00</t>
-  </si>
-  <si>
-    <t>7.349</t>
-  </si>
-  <si>
-    <t>7.711</t>
-  </si>
-  <si>
-    <t>150.14</t>
-  </si>
-  <si>
-    <t>13.599</t>
-  </si>
-  <si>
-    <t>-0.010</t>
-  </si>
-  <si>
-    <t>105.18</t>
-  </si>
-  <si>
-    <t>103.53</t>
-  </si>
-  <si>
-    <t>103.50</t>
-  </si>
-  <si>
-    <t>161.62</t>
-  </si>
-  <si>
     <t>fs</t>
   </si>
   <si>
-    <t>282.289</t>
-  </si>
-  <si>
-    <t>0.9316</t>
-  </si>
-  <si>
-    <t>0.024–2.872</t>
-  </si>
-  <si>
-    <t>0.033–2.882</t>
-  </si>
-  <si>
-    <t>92.56</t>
-  </si>
-  <si>
-    <t>9.2652</t>
-  </si>
-  <si>
-    <t>178.03</t>
-  </si>
-  <si>
-    <t>7.367</t>
-  </si>
-  <si>
-    <t>7.731</t>
-  </si>
-  <si>
-    <t>150.66</t>
-  </si>
-  <si>
-    <t>12.993</t>
-  </si>
-  <si>
-    <t>106.39</t>
-  </si>
-  <si>
-    <t>107.14</t>
-  </si>
-  <si>
-    <t>107.10</t>
-  </si>
-  <si>
-    <t>161.72</t>
-  </si>
-  <si>
-    <t>161.71</t>
-  </si>
-  <si>
     <t>sf</t>
   </si>
   <si>
-    <t>286.709</t>
-  </si>
-  <si>
-    <t>0.9461</t>
-  </si>
-  <si>
-    <t>0.047–3.044</t>
-  </si>
-  <si>
-    <t>0.057–3.054</t>
-  </si>
-  <si>
-    <t>92.13</t>
-  </si>
-  <si>
-    <t>9.5363</t>
-  </si>
-  <si>
-    <t>177.99</t>
-  </si>
-  <si>
-    <t>7.405</t>
-  </si>
-  <si>
-    <t>7.756</t>
-  </si>
-  <si>
-    <t>148.60</t>
-  </si>
-  <si>
-    <t>12.752</t>
-  </si>
-  <si>
-    <t>-0.009</t>
-  </si>
-  <si>
-    <t>108.93</t>
-  </si>
-  <si>
-    <t>101.39</t>
-  </si>
-  <si>
-    <t>101.37</t>
-  </si>
-  <si>
-    <t>161.96</t>
-  </si>
-  <si>
     <t>3.0 V</t>
   </si>
   <si>
-    <t>3.000</t>
-  </si>
-  <si>
-    <t>283.103</t>
-  </si>
-  <si>
-    <t>0.8493</t>
-  </si>
-  <si>
-    <t>1.5000</t>
-  </si>
-  <si>
-    <t>0.036–2.658</t>
-  </si>
-  <si>
-    <t>0.045–2.668</t>
-  </si>
-  <si>
-    <t>91.86</t>
-  </si>
-  <si>
-    <t>9.3668</t>
-  </si>
-  <si>
-    <t>7.318</t>
-  </si>
-  <si>
-    <t>7.725</t>
-  </si>
-  <si>
-    <t>152.49</t>
-  </si>
-  <si>
-    <t>12.874</t>
-  </si>
-  <si>
-    <t>-0.004</t>
-  </si>
-  <si>
-    <t>105.10</t>
-  </si>
-  <si>
-    <t>104.40</t>
-  </si>
-  <si>
-    <t>104.37</t>
-  </si>
-  <si>
-    <t>161.79</t>
-  </si>
-  <si>
     <t>3.6 V</t>
   </si>
   <si>
-    <t>3.600</t>
-  </si>
-  <si>
-    <t>285.646</t>
-  </si>
-  <si>
-    <t>1.0283</t>
-  </si>
-  <si>
-    <t>1.8000</t>
-  </si>
-  <si>
-    <t>0.030–3.256</t>
-  </si>
-  <si>
-    <t>0.040–3.266</t>
-  </si>
-  <si>
-    <t>93.09</t>
-  </si>
-  <si>
-    <t>9.4315</t>
-  </si>
-  <si>
-    <t>7.419</t>
-  </si>
-  <si>
-    <t>7.763</t>
-  </si>
-  <si>
-    <t>148.45</t>
-  </si>
-  <si>
-    <t>12.889</t>
-  </si>
-  <si>
-    <t>-0.002</t>
-  </si>
-  <si>
-    <t>109.79</t>
-  </si>
-  <si>
-    <t>104.27</t>
-  </si>
-  <si>
-    <t>104.25</t>
-  </si>
-  <si>
-    <t>161.91</t>
-  </si>
-  <si>
     <t>-40 C</t>
   </si>
   <si>
-    <t>273.069</t>
-  </si>
-  <si>
-    <t>0.9011</t>
-  </si>
-  <si>
-    <t>0.019–2.797</t>
-  </si>
-  <si>
-    <t>0.029–2.807</t>
-  </si>
-  <si>
-    <t>93.68</t>
-  </si>
-  <si>
-    <t>11.3132</t>
-  </si>
-  <si>
-    <t>7.436</t>
-  </si>
-  <si>
-    <t>7.779</t>
-  </si>
-  <si>
-    <t>145.94</t>
-  </si>
-  <si>
-    <t>11.945</t>
-  </si>
-  <si>
-    <t>-0.008</t>
-  </si>
-  <si>
-    <t>109.23</t>
-  </si>
-  <si>
-    <t>104.58</t>
-  </si>
-  <si>
-    <t>104.56</t>
-  </si>
-  <si>
-    <t>163.59</t>
-  </si>
-  <si>
     <t>125 C</t>
   </si>
   <si>
-    <t>297.562</t>
-  </si>
-  <si>
-    <t>0.9820</t>
-  </si>
-  <si>
-    <t>0.056–3.189</t>
-  </si>
-  <si>
-    <t>0.066–3.199</t>
-  </si>
-  <si>
-    <t>90.57</t>
-  </si>
-  <si>
-    <t>7.5919</t>
-  </si>
-  <si>
-    <t>7.297</t>
-  </si>
-  <si>
-    <t>7.676</t>
-  </si>
-  <si>
-    <t>154.85</t>
-  </si>
-  <si>
-    <t>14.073</t>
-  </si>
-  <si>
-    <t>106.52</t>
-  </si>
-  <si>
-    <t>102.10</t>
-  </si>
-  <si>
-    <t>102.07</t>
-  </si>
-  <si>
-    <t>160.00</t>
-  </si>
-  <si>
-    <t>66.18</t>
-  </si>
-  <si>
-    <t>66.68</t>
-  </si>
-  <si>
-    <t>65.56</t>
-  </si>
-  <si>
-    <t>67.13</t>
-  </si>
-  <si>
-    <t>65.12</t>
-  </si>
-  <si>
-    <t>66.10</t>
-  </si>
-  <si>
-    <t>66.25</t>
-  </si>
-  <si>
-    <t>65.98</t>
-  </si>
-  <si>
-    <t>66.58</t>
-  </si>
-  <si>
-    <t>AVDD</t>
+    <t>0.005–3.160</t>
+  </si>
+  <si>
+    <t>CLoad (fixed)</t>
+  </si>
+  <si>
+    <t>280.343</t>
+  </si>
+  <si>
+    <t>1.0910</t>
+  </si>
+  <si>
+    <t>0.000–2.180</t>
+  </si>
+  <si>
+    <t>107.59</t>
+  </si>
+  <si>
+    <t>0.047–2.881</t>
   </si>
 </sst>
 </file>
@@ -688,20 +298,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="true"/>
     <col min="2" max="2" width="6.85546875" customWidth="true"/>
     <col min="3" max="3" width="12.7109375" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="12.7109375" customWidth="true"/>
-    <col min="6" max="6" width="12.7109375" customWidth="true"/>
-    <col min="7" max="7" width="12.7109375" customWidth="true"/>
-    <col min="8" max="8" width="12.7109375" customWidth="true"/>
-    <col min="9" max="9" width="12.7109375" customWidth="true"/>
-    <col min="10" max="10" width="12.7109375" customWidth="true"/>
-    <col min="11" max="11" width="12.7109375" customWidth="true"/>
+    <col min="4" max="4" width="4.7109375" customWidth="true"/>
+    <col min="5" max="5" width="4.7109375" customWidth="true"/>
+    <col min="6" max="6" width="4.7109375" customWidth="true"/>
+    <col min="7" max="7" width="4.7109375" customWidth="true"/>
+    <col min="8" max="8" width="5.42578125" customWidth="true"/>
+    <col min="9" max="9" width="5.42578125" customWidth="true"/>
+    <col min="10" max="10" width="5.42578125" customWidth="true"/>
+    <col min="11" max="11" width="5.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -709,69 +319,69 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>169</v>
+        <v>71</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>185</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>209</v>
+        <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -779,34 +389,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4">
@@ -814,34 +424,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>135</v>
+        <v>65</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>170</v>
+        <v>65</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>186</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5">
@@ -849,34 +459,34 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>118</v>
+        <v>65</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>171</v>
+        <v>65</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>187</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -884,34 +494,34 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7">
@@ -919,34 +529,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>137</v>
+        <v>65</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>155</v>
+        <v>65</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
@@ -954,34 +564,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>119</v>
+        <v>65</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>172</v>
+        <v>65</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>188</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -989,34 +599,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>139</v>
+        <v>65</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>157</v>
+        <v>65</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>173</v>
+        <v>65</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>189</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -1024,34 +634,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>140</v>
+        <v>65</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>158</v>
+        <v>65</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>190</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -1059,34 +669,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>122</v>
+        <v>65</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>191</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -1094,69 +704,69 @@
         <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>201</v>
+        <v>65</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>202</v>
+        <v>65</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>204</v>
+        <v>65</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>205</v>
+        <v>65</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>206</v>
+        <v>65</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>207</v>
+        <v>65</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>208</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -1164,34 +774,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>107</v>
+        <v>65</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>176</v>
+        <v>65</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>192</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -1199,34 +809,34 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>161</v>
+        <v>65</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>177</v>
+        <v>65</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>193</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1234,34 +844,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>144</v>
+        <v>65</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>162</v>
+        <v>65</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>178</v>
+        <v>65</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>194</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1269,34 +879,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>93</v>
+        <v>65</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>127</v>
+        <v>65</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>145</v>
+        <v>65</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>195</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18">
@@ -1304,34 +914,34 @@
         <v>17</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>128</v>
+        <v>65</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>164</v>
+        <v>65</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19">
@@ -1339,34 +949,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1374,34 +984,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
@@ -1409,34 +1019,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22">
@@ -1444,34 +1054,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>111</v>
+        <v>65</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>147</v>
+        <v>65</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>165</v>
+        <v>65</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>181</v>
+        <v>65</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>196</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
@@ -1479,34 +1089,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>197</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24">
@@ -1514,34 +1124,34 @@
         <v>23</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>197</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -1549,34 +1159,34 @@
         <v>24</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>166</v>
+        <v>65</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>197</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26">
@@ -1584,34 +1194,34 @@
         <v>25</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>149</v>
+        <v>65</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>167</v>
+        <v>65</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27">
@@ -1619,34 +1229,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
     </row>
     <row r="28">
@@ -1654,34 +1264,34 @@
         <v>27</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -1689,34 +1299,34 @@
         <v>28</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>199</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
@@ -1724,69 +1334,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>63</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="H30" s="0" t="s">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>168</v>
+        <v>65</v>
       </c>
       <c r="J30" s="0" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="K30" s="0" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="E31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="G31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="I31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="J31" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="K31" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Measurement_Results/IC_Simulation/SE_OTA/SE_OTA_Full_PVT_Table.xlsx
+++ b/Measurement_Results/IC_Simulation/SE_OTA/SE_OTA_Full_PVT_Table.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6930" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="8244" uniqueCount="125">
   <si>
     <t>Parameter</t>
   </si>
@@ -51,208 +51,343 @@
     <t>Phase margin</t>
   </si>
   <si>
+    <t>CLoad (fixed)</t>
+  </si>
+  <si>
+    <t>Slew rate rising</t>
+  </si>
+  <si>
+    <t>Slew rate falling</t>
+  </si>
+  <si>
+    <t>Settling time</t>
+  </si>
+  <si>
+    <t>Input-referred noise</t>
+  </si>
+  <si>
+    <t>Input offset</t>
+  </si>
+  <si>
+    <t>CMRR @ 1 Hz</t>
+  </si>
+  <si>
+    <t>CMRR @ 60 Hz</t>
+  </si>
+  <si>
+    <t>CMRR @ 150 Hz</t>
+  </si>
+  <si>
+    <t>CMRR @ 1 kHz</t>
+  </si>
+  <si>
+    <t>PSRR+ @ 1 Hz</t>
+  </si>
+  <si>
+    <t>PSRR+ @ 60 Hz</t>
+  </si>
+  <si>
+    <t>PSRR+ @ 150 Hz</t>
+  </si>
+  <si>
+    <t>PSRR+ @ 1 kHz</t>
+  </si>
+  <si>
+    <t>PSRR- @ 1 Hz</t>
+  </si>
+  <si>
+    <t>PSRR- @ 60 Hz</t>
+  </si>
+  <si>
+    <t>PSRR- @ 150 Hz</t>
+  </si>
+  <si>
+    <t>PSRR- @ 1 kHz</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>uA</t>
+  </si>
+  <si>
+    <t>mW</t>
+  </si>
+  <si>
+    <t>dB</t>
+  </si>
+  <si>
+    <t>MHz</t>
+  </si>
+  <si>
+    <t>deg</t>
+  </si>
+  <si>
+    <t>pF</t>
+  </si>
+  <si>
+    <t>V/us</t>
+  </si>
+  <si>
+    <t>ns</t>
+  </si>
+  <si>
+    <t>uVrms</t>
+  </si>
+  <si>
+    <t>mV</t>
+  </si>
+  <si>
+    <t>Nominal</t>
+  </si>
+  <si>
+    <t>3.300</t>
+  </si>
+  <si>
+    <t>40.000</t>
+  </si>
+  <si>
+    <t>280.343</t>
+  </si>
+  <si>
+    <t>0.9251</t>
+  </si>
+  <si>
+    <t>1.6500</t>
+  </si>
+  <si>
+    <t>1.0910</t>
+  </si>
+  <si>
+    <t>0.000–2.180</t>
+  </si>
+  <si>
+    <t>0.047–2.881</t>
+  </si>
+  <si>
+    <t>92.54</t>
+  </si>
+  <si>
+    <t>9.5191</t>
+  </si>
+  <si>
+    <t>66.35</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>7.470</t>
+  </si>
+  <si>
+    <t>7.752</t>
+  </si>
+  <si>
+    <t>147.07</t>
+  </si>
+  <si>
+    <t>12.594</t>
+  </si>
+  <si>
+    <t>0.253</t>
+  </si>
+  <si>
+    <t>107.86</t>
+  </si>
+  <si>
+    <t>107.60</t>
+  </si>
+  <si>
+    <t>107.59</t>
+  </si>
+  <si>
+    <t>107.56</t>
+  </si>
+  <si>
+    <t>107.61</t>
+  </si>
+  <si>
+    <t>107.58</t>
+  </si>
+  <si>
+    <t>ff</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>ss</t>
+  </si>
+  <si>
+    <t>fs</t>
+  </si>
+  <si>
+    <t>sf</t>
+  </si>
+  <si>
+    <t>3.0 V</t>
+  </si>
+  <si>
+    <t>3.6 V</t>
+  </si>
+  <si>
+    <t>-40 C</t>
+  </si>
+  <si>
+    <t>125 C</t>
+  </si>
+  <si>
+    <t>Classification</t>
+  </si>
+  <si>
+    <t>Test condition, not measured</t>
+  </si>
+  <si>
+    <t>Measured</t>
+  </si>
+  <si>
+    <t>Calculated</t>
+  </si>
+  <si>
+    <t>Measured/extracted</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>Supply voltage applied to the OTA.</t>
+  </si>
+  <si>
+    <t>Bias current applied by the testbench.</t>
+  </si>
+  <si>
+    <t>Total current drawn from the AVDD supply at the selected operating condition.</t>
+  </si>
+  <si>
+    <t>Power calculated from AVDD and the measured total current.</t>
+  </si>
+  <si>
+    <t>Common-mode voltage applied to the two OTA inputs.</t>
+  </si>
+  <si>
+    <t>Open-loop DC output voltage with Vin+ = Vin- = Vin,cm, so Vin,diff = 0.</t>
+  </si>
+  <si>
+    <t>Closed-loop input-voltage range over which the output follows the input correctly without clipping or leaving the linear operating region.</t>
+  </si>
+  <si>
+    <t>Closed-loop output-voltage range over which the output follows the input within the selected error limit.</t>
+  </si>
+  <si>
+    <t>Open-loop differential voltage gain measured at low frequency.</t>
+  </si>
+  <si>
+    <t>Frequency where the open-loop differential gain falls to unity.</t>
+  </si>
+  <si>
+    <t>Stability margin determined from the open-loop phase at the UGF.</t>
+  </si>
+  <si>
+    <t>Capacitive load connected to the OTA output.</t>
+  </si>
+  <si>
+    <t>Average output rising speed between 10% and 90% of the output step.</t>
+  </si>
+  <si>
+    <t>Average output falling speed between 90% and 10% of the output step.</t>
+  </si>
+  <si>
+    <t>Time required for the output to enter and remain within the selected error band around the final value.</t>
+  </si>
+  <si>
+    <t>Total RMS noise referred to the OTA input and integrated over the selected frequency range.</t>
+  </si>
+  <si>
+    <t>Vin,diff required to make the open-loop output equal to VDD/2 at the selected Vin,cm.</t>
+  </si>
+  <si>
+    <t>Rejection of common-mode input signals at 1 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of common-mode input signals at 60 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of common-mode input signals at 150 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of common-mode input signals at 1 kHz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVDD supply variation at 1 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVDD supply variation at 60 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVDD supply variation at 150 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVDD supply variation at 1 kHz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVSS supply variation at 1 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVSS supply variation at 60 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVSS supply variation at 150 Hz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>Rejection of AVSS supply variation at 1 kHz relative to the differential gain.</t>
+  </si>
+  <si>
+    <t>0.045–2.879</t>
+  </si>
+  <si>
+    <t>0.038–2.957</t>
+  </si>
+  <si>
+    <t>0.043–2.962</t>
+  </si>
+  <si>
+    <t>7.463</t>
+  </si>
+  <si>
+    <t>7.748</t>
+  </si>
+  <si>
+    <t>150.07</t>
+  </si>
+  <si>
     <t>CLoad</t>
   </si>
   <si>
-    <t>Slew rate rising</t>
-  </si>
-  <si>
-    <t>Slew rate falling</t>
-  </si>
-  <si>
-    <t>Settling time</t>
-  </si>
-  <si>
-    <t>Input-referred noise</t>
-  </si>
-  <si>
-    <t>Input offset</t>
-  </si>
-  <si>
-    <t>CMRR @ 1 Hz</t>
-  </si>
-  <si>
-    <t>CMRR @ 60 Hz</t>
-  </si>
-  <si>
-    <t>CMRR @ 150 Hz</t>
-  </si>
-  <si>
-    <t>CMRR @ 1 kHz</t>
-  </si>
-  <si>
-    <t>PSRR+ @ 1 Hz</t>
-  </si>
-  <si>
-    <t>PSRR+ @ 60 Hz</t>
-  </si>
-  <si>
-    <t>PSRR+ @ 150 Hz</t>
-  </si>
-  <si>
-    <t>PSRR+ @ 1 kHz</t>
-  </si>
-  <si>
-    <t>PSRR- @ 1 Hz</t>
-  </si>
-  <si>
-    <t>PSRR- @ 60 Hz</t>
-  </si>
-  <si>
-    <t>PSRR- @ 150 Hz</t>
-  </si>
-  <si>
-    <t>PSRR- @ 1 kHz</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>uA</t>
-  </si>
-  <si>
-    <t>mW</t>
-  </si>
-  <si>
-    <t>dB</t>
-  </si>
-  <si>
-    <t>MHz</t>
-  </si>
-  <si>
-    <t>deg</t>
-  </si>
-  <si>
-    <t>pF</t>
-  </si>
-  <si>
-    <t>V/us</t>
-  </si>
-  <si>
-    <t>ns</t>
-  </si>
-  <si>
-    <t>uVrms</t>
-  </si>
-  <si>
-    <t>mV</t>
-  </si>
-  <si>
-    <t>Nominal</t>
-  </si>
-  <si>
-    <t>3.300</t>
-  </si>
-  <si>
-    <t>40.000</t>
-  </si>
-  <si>
-    <t>280.345</t>
-  </si>
-  <si>
-    <t>0.9251</t>
-  </si>
-  <si>
-    <t>1.6500</t>
-  </si>
-  <si>
-    <t>0.000–2.440</t>
-  </si>
-  <si>
-    <t>0.041–2.998</t>
-  </si>
-  <si>
-    <t>92.54</t>
-  </si>
-  <si>
-    <t>9.5191</t>
-  </si>
-  <si>
-    <t>66.35</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>7.470</t>
-  </si>
-  <si>
-    <t>7.752</t>
-  </si>
-  <si>
-    <t>147.07</t>
-  </si>
-  <si>
-    <t>12.594</t>
-  </si>
-  <si>
-    <t>0.253</t>
-  </si>
-  <si>
-    <t>107.86</t>
-  </si>
-  <si>
-    <t>107.60</t>
-  </si>
-  <si>
-    <t>107.56</t>
-  </si>
-  <si>
-    <t>107.61</t>
-  </si>
-  <si>
-    <t>107.58</t>
-  </si>
-  <si>
-    <t>ff</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>ss</t>
-  </si>
-  <si>
-    <t>fs</t>
-  </si>
-  <si>
-    <t>sf</t>
-  </si>
-  <si>
-    <t>3.0 V</t>
-  </si>
-  <si>
-    <t>3.6 V</t>
-  </si>
-  <si>
-    <t>-40 C</t>
-  </si>
-  <si>
-    <t>125 C</t>
-  </si>
-  <si>
-    <t>0.005–3.160</t>
-  </si>
-  <si>
-    <t>CLoad (fixed)</t>
-  </si>
-  <si>
-    <t>280.343</t>
-  </si>
-  <si>
-    <t>1.0910</t>
-  </si>
-  <si>
-    <t>0.000–2.180</t>
-  </si>
-  <si>
-    <t>107.59</t>
-  </si>
-  <si>
-    <t>0.047–2.881</t>
+    <t>Input CM low</t>
+  </si>
+  <si>
+    <t>Input CM high</t>
+  </si>
+  <si>
+    <t>Output swing low</t>
+  </si>
+  <si>
+    <t>Output swing high</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>2.130</t>
+  </si>
+  <si>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>2.881</t>
   </si>
 </sst>
 </file>
@@ -298,12 +433,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="true"/>
     <col min="2" max="2" width="6.85546875" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="8.7109375" customWidth="true"/>
     <col min="4" max="4" width="4.7109375" customWidth="true"/>
     <col min="5" max="5" width="4.7109375" customWidth="true"/>
     <col min="6" max="6" width="4.7109375" customWidth="true"/>
@@ -312,6 +447,8 @@
     <col min="9" max="9" width="5.42578125" customWidth="true"/>
     <col min="10" max="10" width="5.42578125" customWidth="true"/>
     <col min="11" max="11" width="5.7109375" customWidth="true"/>
+    <col min="12" max="12" width="5.42578125" customWidth="true"/>
+    <col min="13" max="13" width="5.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -325,28 +462,34 @@
         <v>42</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>72</v>
+        <v>74</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="0" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -360,28 +503,34 @@
         <v>43</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L2" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -395,28 +544,34 @@
         <v>44</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L3" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M3" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -427,31 +582,37 @@
         <v>32</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L4" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -465,28 +626,34 @@
         <v>46</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L5" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M5" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -500,28 +667,34 @@
         <v>47</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L6" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M6" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7">
@@ -532,561 +705,657 @@
         <v>31</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L7" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M7" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>7</v>
+        <v>117</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K8" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L8" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M8" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K9" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L9" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K10" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L10" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M10" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>51</v>
+        <v>124</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K11" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L11" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K12" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L12" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M12" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>74</v>
+        <v>10</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="H13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="J13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="K13" s="0" t="s">
-        <v>53</v>
+        <v>67</v>
+      </c>
+      <c r="L13" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="M13" s="0" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K14" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L14" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M14" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>14</v>
+        <v>116</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="I15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="J15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="K15" s="0" t="s">
-        <v>65</v>
+        <v>54</v>
+      </c>
+      <c r="L15" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M15" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K16" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L16" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M16" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K17" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L17" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>58</v>
+        <v>115</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K18" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L18" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M18" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K19" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L19" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M19" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C20" s="0" t="s">
         <v>59</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K20" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L20" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M20" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B21" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K21" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L21" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K22" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L22" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M22" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="0" t="s">
         <v>34</v>
@@ -1095,33 +1364,39 @@
         <v>60</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K23" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L23" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M23" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>34</v>
@@ -1130,68 +1405,80 @@
         <v>60</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K24" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L24" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M24" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B25" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K25" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L25" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M25" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>34</v>
@@ -1200,33 +1487,39 @@
         <v>61</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K26" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L26" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M26" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" s="0" t="s">
         <v>34</v>
@@ -1235,133 +1528,227 @@
         <v>62</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K27" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L27" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M27" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K28" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L28" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M28" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B29" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K29" s="0" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="L29" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M29" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B30" s="0" t="s">
         <v>34</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="I30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="J30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="K30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="L30" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="M30" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="J31" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="K31" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="E30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="G30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="I30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="J30" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="K30" s="0" t="s">
-        <v>65</v>
+      <c r="D32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="F32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="G32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="J32" s="0" t="s">
+        <v>67</v>
+      </c>
+      <c r="K32" s="0" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
